--- a/data/trans_orig/P16B13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2007 (tasa de respuesta: 98,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3074</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18893</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34805</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1898</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14417</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11063</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14925</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>42898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17731</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>13394</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33248</t>
+          <t>33154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4597</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6697</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>75049</t>
+          <t>75807</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84577</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107798</t>
+          <t>108176</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117503</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>188423</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>200356</t>
+          <t>200197</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>9670</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>16524</t>
+          <t>17171</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15911</t>
+          <t>15976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18458</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>23352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34335</t>
+          <t>34224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>13431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>16939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>26226</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45834</t>
+          <t>46470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57218</t>
+          <t>57222</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11995</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23528</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32858</t>
+          <t>32335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5826</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13499</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23157</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18727</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34148</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54820</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30922</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51290</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120311</t>
+          <t>120219</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>135496</t>
+          <t>134559</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>182076</t>
+          <t>182299</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189201</t>
+          <t>189197</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>305713</t>
+          <t>306978</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>322735</t>
+          <t>322831</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4767</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>23381</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016</t>
+          <t>Porcentaje de medicinas para alteraciones digestivas recetados en 2016 (tasa de respuesta: 97,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8609</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26172</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12449</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1806</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9316</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>24011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>36307</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7423</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>9042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,29%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1722</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25678</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>48663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7505</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12355</t>
+          <t>13346</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39381</t>
+          <t>39130</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,35%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>84259</t>
+          <t>82754</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96038</t>
+          <t>96227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129107</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>138000</t>
+          <t>137993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>218352</t>
+          <t>218348</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>232463</t>
+          <t>232777</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1683</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13651</t>
+          <t>15156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>964</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/P16B13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16B13-Provincia-trans_orig.xlsx
@@ -732,7 +732,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3994</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14770</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,56%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,85%</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42898</t>
+          <t>42185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6716</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,73%</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33154</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>75807</t>
+          <t>75932</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>84582</t>
+          <t>84579</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>108176</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>117503</t>
+          <t>117488</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>187776</t>
+          <t>188176</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>200197</t>
+          <t>200566</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>16771</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23352</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>34151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>92,84%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2349</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>12900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>46539</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57222</t>
+          <t>57214</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24892</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32335</t>
+          <t>33173</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>120219</t>
+          <t>119434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>134559</t>
+          <t>134738</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>182299</t>
+          <t>182112</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189197</t>
+          <t>189200</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>306978</t>
+          <t>306537</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>322831</t>
+          <t>322736</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23822</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7413,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>17018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>24840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24011</t>
+          <t>23753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36307</t>
+          <t>36272</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>38,85%</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>25159</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48663</t>
+          <t>48133</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -9554,7 +9554,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39130</t>
+          <t>39018</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7152</t>
+          <t>9571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,59%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>82754</t>
+          <t>83180</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96227</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129934</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>137993</t>
+          <t>138012</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>218348</t>
+          <t>218329</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>232777</t>
+          <t>232549</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>15156</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4090</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>18538</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
